--- a/tests/fixtures/office_corpus/xlsx/07-chart-cached-series.xlsx
+++ b/tests/fixtures/office_corpus/xlsx/07-chart-cached-series.xlsx
@@ -152,6 +152,12 @@
           <tx>
             <strRef>
               <f>'Data'!B1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Revenue</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -167,6 +173,19 @@
           <val>
             <numRef>
               <f>'Data'!$B$2:$B$4</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="3"/>
+                <pt idx="0">
+                  <v>2</v>
+                </pt>
+                <pt idx="1">
+                  <v>3</v>
+                </pt>
+                <pt idx="2">
+                  <v>5</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
         </ser>
